--- a/02_DIA_inicio_2026_analisis_assets/ranking_establecimientos_desafios.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/ranking_establecimientos_desafios.xlsx
@@ -409,7 +409,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colegio Hernan Olguin</t>
+          <t>Colegio Hernán Olguín</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Escuela Basica Bernardo O´Higgins</t>
+          <t>Escuela Básica Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Escuela Basica Villa La Cultura</t>
+          <t>Escuela Básica Villa La Cultura</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liceo Araucania</t>
+          <t>Liceo Araucanía</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Escuela De Parvulos Rayito De Luz</t>
+          <t>Escuela De Párvulos Rayito De Luz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Escuela Territorio Antartico</t>
+          <t>Escuela Territorio Antártico</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1028,13 +1028,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29474DB-E10D-4C48-9C3E-182706D11A1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29C26755-481C-46AD-8733-DDD2F0FBE7DB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{504A8AEE-0877-4F2F-961B-FE665EBE1380}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC034D07-1881-456C-8FFB-32F60D80AB5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDA068E6-A9F0-4C4B-A6D8-BA7D73C80696}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30DF8DA3-C08F-44B8-B1E3-660726EF8AAC}"/>
 </file>